--- a/Data/g17.1.xlsx
+++ b/Data/g17.1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,16 +718,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01/01/2004</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.40000000000001</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="21">
@@ -738,11 +738,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2004</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.90000000000001</v>
+        <v>22.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -753,11 +753,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20.7</v>
+        <v>21.90000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -768,11 +768,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19.90000000000001</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="24">
@@ -783,11 +783,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>19.40000000000001</v>
+        <v>19.90000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -798,11 +798,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01/01/2009</t>
+          <t>01/01/2008</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18.7</v>
+        <v>19.40000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -813,11 +813,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2009</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.8</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="27">
@@ -828,11 +828,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.40000000000001</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="28">
@@ -843,11 +843,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01/01/2013</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.90000000000001</v>
+        <v>17.40000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -858,11 +858,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.59999999999999</v>
+        <v>16.90000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -873,11 +873,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.2</v>
+        <v>16.59999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -888,11 +888,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="32">
@@ -903,11 +903,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="33">
@@ -918,11 +918,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="34">
@@ -933,11 +933,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="35">
@@ -948,11 +948,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
@@ -963,11 +963,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="37">
@@ -978,41 +978,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01/01/2004</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>19.40000000000001</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>19.7</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="40">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2004</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>18.2</v>
+        <v>19.40000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1038,11 +1038,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>16.8</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="42">
@@ -1053,11 +1053,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.90000000000001</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="43">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01/01/2009</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="44">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2008</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16</v>
+        <v>16.90000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1098,11 +1098,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2009</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="46">
@@ -1113,11 +1113,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01/01/2013</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.09999999999999</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="48">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.59999999999999</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>13.9</v>
+        <v>17.09999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -1173,11 +1173,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>13.7</v>
+        <v>15.59999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="52">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>12.6</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="53">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11.2</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="55">
@@ -1248,11 +1248,56 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C57" t="n">
         <v>10.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>10.3</v>
       </c>
     </row>
   </sheetData>
